--- a/www/flightdata/xlsx/eoss-299.xlsx
+++ b/www/flightdata/xlsx/eoss-299.xlsx
@@ -3219,7 +3219,7 @@
         <v>28377.49</v>
       </c>
       <c r="I2">
-        <v>538</v>
+        <v>400</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
